--- a/3021 материали номенклатури БН - Хати.xlsx
+++ b/3021 материали номенклатури БН - Хати.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\production_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E8DBFF3-F453-4939-B379-1B80B555A444}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D4A7BCB-405B-42D6-9C6D-E395E564A55E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{F75FC252-12BF-4BEB-B1BA-3843060377DB}"/>
+    <workbookView xWindow="0" yWindow="300" windowWidth="23256" windowHeight="12576" xr2:uid="{F75FC252-12BF-4BEB-B1BA-3843060377DB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23291,7 +23291,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -23301,6 +23301,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -23356,7 +23362,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -23374,6 +23380,14 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -23439,17 +23453,9 @@
   <autoFilter ref="A1:E2121" xr:uid="{3EDDB37F-12F5-462D-A43E-73146A888443}">
     <filterColumn colId="4">
       <filters>
-        <filter val="ALUMINIUM PROFILE FOR SAO"/>
-        <filter val="BLACK SAO PIN - FIX LEG"/>
-        <filter val="BLACK SAO WITH 6 LOCATION"/>
-        <filter val="Brico PVC corner profile 15x15x2m white - satin 649324"/>
-        <filter val="CORNER PROFILE PVC 10x10/2 m WHITE SATIN"/>
-        <filter val="PVC TAPE TESA 20 M/19 MM BLACK"/>
-        <filter val="SA40 MARKER PIN"/>
-        <filter val="SA90 BLUE MARKER PIN"/>
-        <filter val="SA90-B BLUE MARKER PIN"/>
-        <filter val="SAO HOLDER WITH 12 YAZAKI TYPE PIN"/>
-        <filter val="YAZAKI TYPE SAO WITH PIN"/>
+        <filter val="SILICON WIRE HOLDER GREY"/>
+        <filter val="WIRE HOLDER LEG"/>
+        <filter val="Wire Holder U30"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -24510,7 +24516,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="45" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
         <v>172</v>
       </c>
@@ -25802,7 +25808,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" s="1" t="s">
         <v>463</v>
       </c>
@@ -27451,7 +27457,7 @@
         <v>828</v>
       </c>
     </row>
-    <row r="218" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A218" s="1" t="s">
         <v>829</v>
       </c>
@@ -33877,7 +33883,7 @@
         <v>2238</v>
       </c>
     </row>
-    <row r="596" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="596" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A596" s="1" t="s">
         <v>2239</v>
       </c>
@@ -34523,7 +34529,7 @@
         <v>2381</v>
       </c>
     </row>
-    <row r="634" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="634" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A634" s="1" t="s">
         <v>2383</v>
       </c>
@@ -35577,7 +35583,7 @@
         <v>2599</v>
       </c>
     </row>
-    <row r="696" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="696" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A696" s="1" t="s">
         <v>2601</v>
       </c>
@@ -41697,7 +41703,7 @@
         <v>3744</v>
       </c>
     </row>
-    <row r="1056" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1056" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1056" s="1" t="s">
         <v>3746</v>
       </c>
@@ -50857,71 +50863,71 @@
         <v>5703</v>
       </c>
     </row>
-    <row r="1595" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1595" s="1" t="s">
+    <row r="1595" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1595" s="9" t="s">
         <v>5705</v>
       </c>
-      <c r="B1595" s="1" t="s">
+      <c r="B1595" s="9" t="s">
         <v>5706</v>
       </c>
-      <c r="C1595" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1595" s="2" t="s">
+      <c r="C1595" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1595" s="10" t="s">
         <v>5708</v>
       </c>
-      <c r="E1595" s="4" t="s">
+      <c r="E1595" s="11" t="s">
         <v>5707</v>
       </c>
     </row>
-    <row r="1596" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1596" s="1" t="s">
+    <row r="1596" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1596" s="9" t="s">
         <v>5709</v>
       </c>
-      <c r="B1596" s="1" t="s">
+      <c r="B1596" s="9" t="s">
         <v>5710</v>
       </c>
-      <c r="C1596" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1596" s="2" t="s">
+      <c r="C1596" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1596" s="10" t="s">
         <v>5712</v>
       </c>
-      <c r="E1596" s="4" t="s">
+      <c r="E1596" s="11" t="s">
         <v>5711</v>
       </c>
     </row>
-    <row r="1597" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1597" s="1" t="s">
+    <row r="1597" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1597" s="9" t="s">
         <v>5713</v>
       </c>
-      <c r="B1597" s="1" t="s">
+      <c r="B1597" s="9" t="s">
         <v>5714</v>
       </c>
-      <c r="C1597" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1597" s="2" t="s">
+      <c r="C1597" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1597" s="10" t="s">
         <v>5716</v>
       </c>
-      <c r="E1597" s="4" t="s">
+      <c r="E1597" s="11" t="s">
         <v>5715</v>
       </c>
     </row>
-    <row r="1598" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1598" s="1" t="s">
+    <row r="1598" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1598" s="9" t="s">
         <v>5717</v>
       </c>
-      <c r="B1598" s="1" t="s">
+      <c r="B1598" s="9" t="s">
         <v>5718</v>
       </c>
-      <c r="C1598" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1598" s="2" t="s">
+      <c r="C1598" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1598" s="10" t="s">
         <v>5719</v>
       </c>
-      <c r="E1598" s="4" t="s">
+      <c r="E1598" s="11" t="s">
         <v>5718</v>
       </c>
     </row>
@@ -51010,7 +51016,7 @@
         <v>5737</v>
       </c>
     </row>
-    <row r="1604" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1604" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1604" s="1" t="s">
         <v>5739</v>
       </c>
@@ -51826,37 +51832,37 @@
         <v>5928</v>
       </c>
     </row>
-    <row r="1652" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1652" s="1" t="s">
+    <row r="1652" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1652" s="9" t="s">
         <v>5930</v>
       </c>
-      <c r="B1652" s="1" t="s">
+      <c r="B1652" s="9" t="s">
         <v>5931</v>
       </c>
-      <c r="C1652" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1652" s="2" t="s">
+      <c r="C1652" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1652" s="10" t="s">
         <v>5933</v>
       </c>
-      <c r="E1652" s="4" t="s">
+      <c r="E1652" s="11" t="s">
         <v>5932</v>
       </c>
     </row>
-    <row r="1653" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1653" s="1" t="s">
+    <row r="1653" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1653" s="9" t="s">
         <v>5934</v>
       </c>
-      <c r="B1653" s="1" t="s">
+      <c r="B1653" s="9" t="s">
         <v>5935</v>
       </c>
-      <c r="C1653" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1653" s="2" t="s">
+      <c r="C1653" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1653" s="10" t="s">
         <v>5937</v>
       </c>
-      <c r="E1653" s="4" t="s">
+      <c r="E1653" s="11" t="s">
         <v>5936</v>
       </c>
     </row>
@@ -51945,7 +51951,7 @@
         <v>5956</v>
       </c>
     </row>
-    <row r="1659" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1659" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1659" s="1" t="s">
         <v>5958</v>
       </c>
@@ -52061,20 +52067,20 @@
         <v>5983</v>
       </c>
     </row>
-    <row r="1666" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1666" s="1" t="s">
+    <row r="1666" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1666" s="9" t="s">
         <v>5985</v>
       </c>
-      <c r="B1666" s="1" t="s">
+      <c r="B1666" s="9" t="s">
         <v>5986</v>
       </c>
-      <c r="C1666" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1666" s="2">
+      <c r="C1666" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1666" s="10">
         <v>0</v>
       </c>
-      <c r="E1666" s="4" t="s">
+      <c r="E1666" s="11" t="s">
         <v>5987</v>
       </c>
     </row>
@@ -52095,88 +52101,88 @@
         <v>5990</v>
       </c>
     </row>
-    <row r="1668" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1668" s="1" t="s">
+    <row r="1668" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1668" s="9" t="s">
         <v>5992</v>
       </c>
-      <c r="B1668" s="1" t="s">
+      <c r="B1668" s="9" t="s">
         <v>5993</v>
       </c>
-      <c r="C1668" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1668" s="2" t="s">
+      <c r="C1668" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1668" s="10" t="s">
         <v>5995</v>
       </c>
-      <c r="E1668" s="4" t="s">
+      <c r="E1668" s="11" t="s">
         <v>5994</v>
       </c>
     </row>
-    <row r="1669" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1669" s="1" t="s">
+    <row r="1669" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1669" s="9" t="s">
         <v>5996</v>
       </c>
-      <c r="B1669" s="1" t="s">
+      <c r="B1669" s="9" t="s">
         <v>5997</v>
       </c>
-      <c r="C1669" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1669" s="2" t="s">
+      <c r="C1669" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1669" s="10" t="s">
         <v>5999</v>
       </c>
-      <c r="E1669" s="4" t="s">
+      <c r="E1669" s="11" t="s">
         <v>5998</v>
       </c>
     </row>
-    <row r="1670" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1670" s="1" t="s">
+    <row r="1670" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1670" s="9" t="s">
         <v>6000</v>
       </c>
-      <c r="B1670" s="1" t="s">
+      <c r="B1670" s="9" t="s">
         <v>6001</v>
       </c>
-      <c r="C1670" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1670" s="2" t="s">
+      <c r="C1670" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1670" s="10" t="s">
         <v>6003</v>
       </c>
-      <c r="E1670" s="4" t="s">
+      <c r="E1670" s="11" t="s">
         <v>6002</v>
       </c>
     </row>
-    <row r="1671" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1671" s="1" t="s">
+    <row r="1671" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1671" s="9" t="s">
         <v>6004</v>
       </c>
-      <c r="B1671" s="1" t="s">
+      <c r="B1671" s="9" t="s">
         <v>6005</v>
       </c>
-      <c r="C1671" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1671" s="2" t="s">
+      <c r="C1671" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1671" s="10" t="s">
         <v>6007</v>
       </c>
-      <c r="E1671" s="4" t="s">
+      <c r="E1671" s="11" t="s">
         <v>6006</v>
       </c>
     </row>
-    <row r="1672" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1672" s="1" t="s">
+    <row r="1672" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1672" s="9" t="s">
         <v>6008</v>
       </c>
-      <c r="B1672" s="1" t="s">
+      <c r="B1672" s="9" t="s">
         <v>6009</v>
       </c>
-      <c r="C1672" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1672" s="2" t="s">
+      <c r="C1672" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1672" s="10" t="s">
         <v>6011</v>
       </c>
-      <c r="E1672" s="4" t="s">
+      <c r="E1672" s="11" t="s">
         <v>6010</v>
       </c>
     </row>
@@ -52197,20 +52203,20 @@
         <v>6014</v>
       </c>
     </row>
-    <row r="1674" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1674" s="1" t="s">
+    <row r="1674" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1674" s="9" t="s">
         <v>6016</v>
       </c>
-      <c r="B1674" s="1" t="s">
+      <c r="B1674" s="9" t="s">
         <v>6017</v>
       </c>
-      <c r="C1674" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1674" s="2" t="s">
+      <c r="C1674" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1674" s="10" t="s">
         <v>6019</v>
       </c>
-      <c r="E1674" s="4" t="s">
+      <c r="E1674" s="11" t="s">
         <v>6018</v>
       </c>
     </row>
@@ -52248,139 +52254,139 @@
         <v>6026</v>
       </c>
     </row>
-    <row r="1677" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1677" s="1" t="s">
+    <row r="1677" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1677" s="9" t="s">
         <v>6028</v>
       </c>
-      <c r="B1677" s="1" t="s">
+      <c r="B1677" s="9" t="s">
         <v>6029</v>
       </c>
-      <c r="C1677" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1677" s="2" t="s">
+      <c r="C1677" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1677" s="10" t="s">
         <v>6031</v>
       </c>
-      <c r="E1677" s="4" t="s">
+      <c r="E1677" s="11" t="s">
         <v>6030</v>
       </c>
     </row>
-    <row r="1678" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1678" s="1" t="s">
+    <row r="1678" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1678" s="9" t="s">
         <v>6032</v>
       </c>
-      <c r="B1678" s="1" t="s">
+      <c r="B1678" s="9" t="s">
         <v>6033</v>
       </c>
-      <c r="C1678" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1678" s="2" t="s">
+      <c r="C1678" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1678" s="10" t="s">
         <v>6035</v>
       </c>
-      <c r="E1678" s="4" t="s">
+      <c r="E1678" s="11" t="s">
         <v>6034</v>
       </c>
     </row>
-    <row r="1679" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1679" s="1" t="s">
+    <row r="1679" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1679" s="9" t="s">
         <v>6036</v>
       </c>
-      <c r="B1679" s="1" t="s">
+      <c r="B1679" s="9" t="s">
         <v>6037</v>
       </c>
-      <c r="C1679" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1679" s="2" t="s">
+      <c r="C1679" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1679" s="10" t="s">
         <v>6039</v>
       </c>
-      <c r="E1679" s="4" t="s">
+      <c r="E1679" s="11" t="s">
         <v>6038</v>
       </c>
     </row>
-    <row r="1680" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1680" s="1" t="s">
+    <row r="1680" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1680" s="9" t="s">
         <v>6040</v>
       </c>
-      <c r="B1680" s="1" t="s">
+      <c r="B1680" s="9" t="s">
         <v>6041</v>
       </c>
-      <c r="C1680" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1680" s="2" t="s">
+      <c r="C1680" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1680" s="10" t="s">
         <v>6043</v>
       </c>
-      <c r="E1680" s="4" t="s">
+      <c r="E1680" s="11" t="s">
         <v>6042</v>
       </c>
     </row>
-    <row r="1681" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1681" s="1" t="s">
+    <row r="1681" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1681" s="9" t="s">
         <v>6044</v>
       </c>
-      <c r="B1681" s="1" t="s">
+      <c r="B1681" s="9" t="s">
         <v>6045</v>
       </c>
-      <c r="C1681" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1681" s="2" t="s">
+      <c r="C1681" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1681" s="10" t="s">
         <v>6047</v>
       </c>
-      <c r="E1681" s="4" t="s">
+      <c r="E1681" s="11" t="s">
         <v>6046</v>
       </c>
     </row>
-    <row r="1682" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1682" s="1" t="s">
+    <row r="1682" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1682" s="9" t="s">
         <v>6048</v>
       </c>
-      <c r="B1682" s="1" t="s">
+      <c r="B1682" s="9" t="s">
         <v>6049</v>
       </c>
-      <c r="C1682" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1682" s="2" t="s">
+      <c r="C1682" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1682" s="10" t="s">
         <v>6050</v>
       </c>
-      <c r="E1682" s="4" t="s">
+      <c r="E1682" s="11" t="s">
         <v>6046</v>
       </c>
     </row>
-    <row r="1683" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1683" s="1" t="s">
+    <row r="1683" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1683" s="9" t="s">
         <v>6051</v>
       </c>
-      <c r="B1683" s="1" t="s">
+      <c r="B1683" s="9" t="s">
         <v>6052</v>
       </c>
-      <c r="C1683" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1683" s="2" t="s">
+      <c r="C1683" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1683" s="10" t="s">
         <v>6054</v>
       </c>
-      <c r="E1683" s="4" t="s">
+      <c r="E1683" s="11" t="s">
         <v>6053</v>
       </c>
     </row>
-    <row r="1684" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1684" s="1" t="s">
+    <row r="1684" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1684" s="9" t="s">
         <v>6055</v>
       </c>
-      <c r="B1684" s="1" t="s">
+      <c r="B1684" s="9" t="s">
         <v>6056</v>
       </c>
-      <c r="C1684" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1684" s="2" t="s">
+      <c r="C1684" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1684" s="10" t="s">
         <v>6058</v>
       </c>
-      <c r="E1684" s="4" t="s">
+      <c r="E1684" s="11" t="s">
         <v>6057</v>
       </c>
     </row>
@@ -52401,20 +52407,20 @@
         <v>6061</v>
       </c>
     </row>
-    <row r="1686" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1686" s="1" t="s">
+    <row r="1686" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1686" s="9" t="s">
         <v>6063</v>
       </c>
-      <c r="B1686" s="1" t="s">
+      <c r="B1686" s="9" t="s">
         <v>6064</v>
       </c>
-      <c r="C1686" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1686" s="2">
+      <c r="C1686" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1686" s="10">
         <v>0</v>
       </c>
-      <c r="E1686" s="4" t="s">
+      <c r="E1686" s="11" t="s">
         <v>6065</v>
       </c>
     </row>
@@ -52452,122 +52458,122 @@
         <v>6072</v>
       </c>
     </row>
-    <row r="1689" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1689" s="1" t="s">
+    <row r="1689" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1689" s="9" t="s">
         <v>6074</v>
       </c>
-      <c r="B1689" s="1" t="s">
+      <c r="B1689" s="9" t="s">
         <v>6075</v>
       </c>
-      <c r="C1689" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1689" s="2" t="s">
+      <c r="C1689" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1689" s="10" t="s">
         <v>6077</v>
       </c>
-      <c r="E1689" s="4" t="s">
+      <c r="E1689" s="11" t="s">
         <v>6076</v>
       </c>
     </row>
-    <row r="1690" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1690" s="1" t="s">
+    <row r="1690" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1690" s="9" t="s">
         <v>6078</v>
       </c>
-      <c r="B1690" s="1" t="s">
+      <c r="B1690" s="9" t="s">
         <v>6079</v>
       </c>
-      <c r="C1690" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1690" s="2" t="s">
+      <c r="C1690" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1690" s="10" t="s">
         <v>6081</v>
       </c>
-      <c r="E1690" s="4" t="s">
+      <c r="E1690" s="11" t="s">
         <v>6080</v>
       </c>
     </row>
-    <row r="1691" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1691" s="1" t="s">
+    <row r="1691" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1691" s="9" t="s">
         <v>6082</v>
       </c>
-      <c r="B1691" s="1" t="s">
+      <c r="B1691" s="9" t="s">
         <v>6083</v>
       </c>
-      <c r="C1691" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1691" s="2" t="s">
+      <c r="C1691" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1691" s="10" t="s">
         <v>6085</v>
       </c>
-      <c r="E1691" s="4" t="s">
+      <c r="E1691" s="11" t="s">
         <v>6084</v>
       </c>
     </row>
-    <row r="1692" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1692" s="1" t="s">
+    <row r="1692" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1692" s="9" t="s">
         <v>6086</v>
       </c>
-      <c r="B1692" s="1" t="s">
+      <c r="B1692" s="9" t="s">
         <v>6087</v>
       </c>
-      <c r="C1692" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1692" s="2" t="s">
+      <c r="C1692" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1692" s="10" t="s">
         <v>6089</v>
       </c>
-      <c r="E1692" s="4" t="s">
+      <c r="E1692" s="11" t="s">
         <v>6088</v>
       </c>
     </row>
-    <row r="1693" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1693" s="1" t="s">
+    <row r="1693" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1693" s="9" t="s">
         <v>6090</v>
       </c>
-      <c r="B1693" s="1" t="s">
+      <c r="B1693" s="9" t="s">
         <v>6091</v>
       </c>
-      <c r="C1693" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1693" s="2" t="s">
+      <c r="C1693" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1693" s="10" t="s">
         <v>6093</v>
       </c>
-      <c r="E1693" s="4" t="s">
+      <c r="E1693" s="11" t="s">
         <v>6092</v>
       </c>
     </row>
-    <row r="1694" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1694" s="1" t="s">
+    <row r="1694" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1694" s="9" t="s">
         <v>6094</v>
       </c>
-      <c r="B1694" s="1" t="s">
+      <c r="B1694" s="9" t="s">
         <v>6095</v>
       </c>
-      <c r="C1694" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1694" s="2" t="s">
+      <c r="C1694" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1694" s="10" t="s">
         <v>6097</v>
       </c>
-      <c r="E1694" s="4" t="s">
+      <c r="E1694" s="11" t="s">
         <v>6096</v>
       </c>
     </row>
-    <row r="1695" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1695" s="1" t="s">
+    <row r="1695" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1695" s="9" t="s">
         <v>6098</v>
       </c>
-      <c r="B1695" s="1" t="s">
+      <c r="B1695" s="9" t="s">
         <v>6099</v>
       </c>
-      <c r="C1695" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1695" s="2" t="s">
+      <c r="C1695" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1695" s="10" t="s">
         <v>6101</v>
       </c>
-      <c r="E1695" s="4" t="s">
+      <c r="E1695" s="11" t="s">
         <v>6100</v>
       </c>
     </row>
@@ -52622,20 +52628,20 @@
         <v>6112</v>
       </c>
     </row>
-    <row r="1699" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1699" s="1" t="s">
+    <row r="1699" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1699" s="9" t="s">
         <v>6114</v>
       </c>
-      <c r="B1699" s="1" t="s">
+      <c r="B1699" s="9" t="s">
         <v>6115</v>
       </c>
-      <c r="C1699" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1699" s="2" t="s">
+      <c r="C1699" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1699" s="10" t="s">
         <v>6117</v>
       </c>
-      <c r="E1699" s="4" t="s">
+      <c r="E1699" s="11" t="s">
         <v>6116</v>
       </c>
     </row>
@@ -52673,7 +52679,7 @@
         <v>6124</v>
       </c>
     </row>
-    <row r="1702" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1702" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1702" s="1" t="s">
         <v>6126</v>
       </c>
@@ -52758,20 +52764,20 @@
         <v>6144</v>
       </c>
     </row>
-    <row r="1707" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1707" s="1" t="s">
+    <row r="1707" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1707" s="9" t="s">
         <v>6146</v>
       </c>
-      <c r="B1707" s="1" t="s">
+      <c r="B1707" s="9" t="s">
         <v>6147</v>
       </c>
-      <c r="C1707" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1707" s="2" t="s">
+      <c r="C1707" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1707" s="10" t="s">
         <v>6149</v>
       </c>
-      <c r="E1707" s="4" t="s">
+      <c r="E1707" s="11" t="s">
         <v>6148</v>
       </c>
     </row>
@@ -52894,20 +52900,20 @@
         <v>6176</v>
       </c>
     </row>
-    <row r="1715" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1715" s="1" t="s">
+    <row r="1715" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1715" s="9" t="s">
         <v>6178</v>
       </c>
-      <c r="B1715" s="1" t="s">
+      <c r="B1715" s="9" t="s">
         <v>6179</v>
       </c>
-      <c r="C1715" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1715" s="2" t="s">
+      <c r="C1715" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1715" s="10" t="s">
         <v>6181</v>
       </c>
-      <c r="E1715" s="4" t="s">
+      <c r="E1715" s="11" t="s">
         <v>6180</v>
       </c>
     </row>
@@ -52928,20 +52934,20 @@
         <v>6184</v>
       </c>
     </row>
-    <row r="1717" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1717" s="1" t="s">
+    <row r="1717" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1717" s="9" t="s">
         <v>6186</v>
       </c>
-      <c r="B1717" s="1" t="s">
+      <c r="B1717" s="9" t="s">
         <v>6187</v>
       </c>
-      <c r="C1717" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1717" s="2" t="s">
+      <c r="C1717" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1717" s="10" t="s">
         <v>6189</v>
       </c>
-      <c r="E1717" s="4" t="s">
+      <c r="E1717" s="11" t="s">
         <v>6188</v>
       </c>
     </row>
@@ -52979,37 +52985,37 @@
         <v>6196</v>
       </c>
     </row>
-    <row r="1720" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1720" s="1" t="s">
+    <row r="1720" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1720" s="9" t="s">
         <v>6198</v>
       </c>
-      <c r="B1720" s="1" t="s">
+      <c r="B1720" s="9" t="s">
         <v>6199</v>
       </c>
-      <c r="C1720" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1720" s="2" t="s">
+      <c r="C1720" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1720" s="10" t="s">
         <v>6201</v>
       </c>
-      <c r="E1720" s="4" t="s">
+      <c r="E1720" s="11" t="s">
         <v>6200</v>
       </c>
     </row>
-    <row r="1721" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1721" s="1" t="s">
+    <row r="1721" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1721" s="9" t="s">
         <v>6202</v>
       </c>
-      <c r="B1721" s="1" t="s">
+      <c r="B1721" s="9" t="s">
         <v>6203</v>
       </c>
-      <c r="C1721" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1721" s="2" t="s">
+      <c r="C1721" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1721" s="10" t="s">
         <v>6205</v>
       </c>
-      <c r="E1721" s="4" t="s">
+      <c r="E1721" s="11" t="s">
         <v>6204</v>
       </c>
     </row>
@@ -53183,37 +53189,37 @@
         <v>6244</v>
       </c>
     </row>
-    <row r="1732" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1732" s="1" t="s">
+    <row r="1732" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1732" s="9" t="s">
         <v>6246</v>
       </c>
-      <c r="B1732" s="1" t="s">
+      <c r="B1732" s="9" t="s">
         <v>6247</v>
       </c>
-      <c r="C1732" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1732" s="2" t="s">
+      <c r="C1732" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1732" s="10" t="s">
         <v>6249</v>
       </c>
-      <c r="E1732" s="4" t="s">
+      <c r="E1732" s="11" t="s">
         <v>6248</v>
       </c>
     </row>
-    <row r="1733" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1733" s="1" t="s">
+    <row r="1733" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1733" s="9" t="s">
         <v>6250</v>
       </c>
-      <c r="B1733" s="1" t="s">
+      <c r="B1733" s="9" t="s">
         <v>6251</v>
       </c>
-      <c r="C1733" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1733" s="2" t="s">
+      <c r="C1733" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1733" s="10" t="s">
         <v>6253</v>
       </c>
-      <c r="E1733" s="4" t="s">
+      <c r="E1733" s="11" t="s">
         <v>6252</v>
       </c>
     </row>
@@ -53319,20 +53325,20 @@
         <v>6276</v>
       </c>
     </row>
-    <row r="1740" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1740" s="1" t="s">
+    <row r="1740" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1740" s="9" t="s">
         <v>6278</v>
       </c>
-      <c r="B1740" s="1" t="s">
+      <c r="B1740" s="9" t="s">
         <v>6279</v>
       </c>
-      <c r="C1740" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1740" s="2" t="s">
+      <c r="C1740" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1740" s="10" t="s">
         <v>6281</v>
       </c>
-      <c r="E1740" s="4" t="s">
+      <c r="E1740" s="11" t="s">
         <v>6280</v>
       </c>
     </row>
@@ -53387,88 +53393,88 @@
         <v>6292</v>
       </c>
     </row>
-    <row r="1744" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1744" s="1" t="s">
+    <row r="1744" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1744" s="9" t="s">
         <v>6294</v>
       </c>
-      <c r="B1744" s="1" t="s">
+      <c r="B1744" s="9" t="s">
         <v>6295</v>
       </c>
-      <c r="C1744" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1744" s="2" t="s">
+      <c r="C1744" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1744" s="10" t="s">
         <v>6297</v>
       </c>
-      <c r="E1744" s="4" t="s">
+      <c r="E1744" s="11" t="s">
         <v>6296</v>
       </c>
     </row>
-    <row r="1745" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1745" s="1" t="s">
+    <row r="1745" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1745" s="9" t="s">
         <v>6298</v>
       </c>
-      <c r="B1745" s="1" t="s">
+      <c r="B1745" s="9" t="s">
         <v>6299</v>
       </c>
-      <c r="C1745" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1745" s="2" t="s">
+      <c r="C1745" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1745" s="10" t="s">
         <v>6301</v>
       </c>
-      <c r="E1745" s="4" t="s">
+      <c r="E1745" s="11" t="s">
         <v>6300</v>
       </c>
     </row>
-    <row r="1746" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1746" s="1" t="s">
+    <row r="1746" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1746" s="9" t="s">
         <v>6302</v>
       </c>
-      <c r="B1746" s="1" t="s">
+      <c r="B1746" s="9" t="s">
         <v>6303</v>
       </c>
-      <c r="C1746" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1746" s="2" t="s">
+      <c r="C1746" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1746" s="10" t="s">
         <v>6305</v>
       </c>
-      <c r="E1746" s="4" t="s">
+      <c r="E1746" s="11" t="s">
         <v>6304</v>
       </c>
     </row>
-    <row r="1747" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1747" s="1" t="s">
+    <row r="1747" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1747" s="9" t="s">
         <v>6306</v>
       </c>
-      <c r="B1747" s="1" t="s">
+      <c r="B1747" s="9" t="s">
         <v>6307</v>
       </c>
-      <c r="C1747" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1747" s="2" t="s">
+      <c r="C1747" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1747" s="10" t="s">
         <v>6309</v>
       </c>
-      <c r="E1747" s="4" t="s">
+      <c r="E1747" s="11" t="s">
         <v>6308</v>
       </c>
     </row>
-    <row r="1748" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1748" s="1" t="s">
+    <row r="1748" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1748" s="9" t="s">
         <v>6310</v>
       </c>
-      <c r="B1748" s="1" t="s">
+      <c r="B1748" s="9" t="s">
         <v>6311</v>
       </c>
-      <c r="C1748" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1748" s="2" t="s">
+      <c r="C1748" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1748" s="10" t="s">
         <v>6313</v>
       </c>
-      <c r="E1748" s="4" t="s">
+      <c r="E1748" s="11" t="s">
         <v>6312</v>
       </c>
     </row>
@@ -53523,54 +53529,54 @@
         <v>6324</v>
       </c>
     </row>
-    <row r="1752" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1752" s="1" t="s">
+    <row r="1752" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1752" s="9" t="s">
         <v>6326</v>
       </c>
-      <c r="B1752" s="1" t="s">
+      <c r="B1752" s="9" t="s">
         <v>6327</v>
       </c>
-      <c r="C1752" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1752" s="2" t="s">
+      <c r="C1752" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1752" s="10" t="s">
         <v>6329</v>
       </c>
-      <c r="E1752" s="4" t="s">
+      <c r="E1752" s="11" t="s">
         <v>6328</v>
       </c>
     </row>
-    <row r="1753" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1753" s="1" t="s">
+    <row r="1753" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1753" s="9" t="s">
         <v>6330</v>
       </c>
-      <c r="B1753" s="1" t="s">
+      <c r="B1753" s="9" t="s">
         <v>6331</v>
       </c>
-      <c r="C1753" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1753" s="2" t="s">
+      <c r="C1753" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1753" s="10" t="s">
         <v>6332</v>
       </c>
-      <c r="E1753" s="4" t="s">
+      <c r="E1753" s="11" t="s">
         <v>6100</v>
       </c>
     </row>
-    <row r="1754" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1754" s="1" t="s">
+    <row r="1754" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1754" s="9" t="s">
         <v>6333</v>
       </c>
-      <c r="B1754" s="1" t="s">
+      <c r="B1754" s="9" t="s">
         <v>6334</v>
       </c>
-      <c r="C1754" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1754" s="2" t="s">
+      <c r="C1754" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1754" s="10" t="s">
         <v>6336</v>
       </c>
-      <c r="E1754" s="4" t="s">
+      <c r="E1754" s="11" t="s">
         <v>6335</v>
       </c>
     </row>
@@ -53591,71 +53597,71 @@
         <v>6339</v>
       </c>
     </row>
-    <row r="1756" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1756" s="1" t="s">
+    <row r="1756" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1756" s="9" t="s">
         <v>6341</v>
       </c>
-      <c r="B1756" s="1" t="s">
+      <c r="B1756" s="9" t="s">
         <v>6342</v>
       </c>
-      <c r="C1756" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1756" s="2" t="s">
+      <c r="C1756" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1756" s="10" t="s">
         <v>6344</v>
       </c>
-      <c r="E1756" s="4" t="s">
+      <c r="E1756" s="11" t="s">
         <v>6343</v>
       </c>
     </row>
-    <row r="1757" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1757" s="1" t="s">
+    <row r="1757" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1757" s="9" t="s">
         <v>6345</v>
       </c>
-      <c r="B1757" s="1" t="s">
+      <c r="B1757" s="9" t="s">
         <v>6346</v>
       </c>
-      <c r="C1757" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1757" s="2" t="s">
+      <c r="C1757" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1757" s="10" t="s">
         <v>6348</v>
       </c>
-      <c r="E1757" s="4" t="s">
+      <c r="E1757" s="11" t="s">
         <v>6347</v>
       </c>
     </row>
-    <row r="1758" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1758" s="1" t="s">
+    <row r="1758" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1758" s="9" t="s">
         <v>6349</v>
       </c>
-      <c r="B1758" s="1" t="s">
+      <c r="B1758" s="9" t="s">
         <v>6350</v>
       </c>
-      <c r="C1758" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1758" s="2" t="s">
+      <c r="C1758" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1758" s="10" t="s">
         <v>6352</v>
       </c>
-      <c r="E1758" s="4" t="s">
+      <c r="E1758" s="11" t="s">
         <v>6351</v>
       </c>
     </row>
-    <row r="1759" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1759" s="1" t="s">
+    <row r="1759" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1759" s="9" t="s">
         <v>6353</v>
       </c>
-      <c r="B1759" s="1" t="s">
+      <c r="B1759" s="9" t="s">
         <v>6354</v>
       </c>
-      <c r="C1759" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1759" s="2" t="s">
+      <c r="C1759" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1759" s="10" t="s">
         <v>6356</v>
       </c>
-      <c r="E1759" s="4" t="s">
+      <c r="E1759" s="11" t="s">
         <v>6355</v>
       </c>
     </row>
@@ -53676,71 +53682,71 @@
         <v>6359</v>
       </c>
     </row>
-    <row r="1761" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1761" s="1" t="s">
+    <row r="1761" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1761" s="9" t="s">
         <v>6361</v>
       </c>
-      <c r="B1761" s="1" t="s">
+      <c r="B1761" s="9" t="s">
         <v>6362</v>
       </c>
-      <c r="C1761" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1761" s="2" t="s">
+      <c r="C1761" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1761" s="10" t="s">
         <v>6364</v>
       </c>
-      <c r="E1761" s="4" t="s">
+      <c r="E1761" s="11" t="s">
         <v>6363</v>
       </c>
     </row>
-    <row r="1762" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1762" s="1" t="s">
+    <row r="1762" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1762" s="9" t="s">
         <v>6365</v>
       </c>
-      <c r="B1762" s="1" t="s">
+      <c r="B1762" s="9" t="s">
         <v>6366</v>
       </c>
-      <c r="C1762" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1762" s="2" t="s">
+      <c r="C1762" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1762" s="10" t="s">
         <v>6368</v>
       </c>
-      <c r="E1762" s="4" t="s">
+      <c r="E1762" s="11" t="s">
         <v>6367</v>
       </c>
     </row>
-    <row r="1763" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1763" s="1" t="s">
+    <row r="1763" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1763" s="9" t="s">
         <v>6369</v>
       </c>
-      <c r="B1763" s="1" t="s">
+      <c r="B1763" s="9" t="s">
         <v>6370</v>
       </c>
-      <c r="C1763" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1763" s="2" t="s">
+      <c r="C1763" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1763" s="10" t="s">
         <v>6372</v>
       </c>
-      <c r="E1763" s="4" t="s">
+      <c r="E1763" s="11" t="s">
         <v>6371</v>
       </c>
     </row>
-    <row r="1764" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1764" s="1" t="s">
+    <row r="1764" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1764" s="9" t="s">
         <v>6373</v>
       </c>
-      <c r="B1764" s="1" t="s">
+      <c r="B1764" s="9" t="s">
         <v>6374</v>
       </c>
-      <c r="C1764" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1764" s="2" t="s">
+      <c r="C1764" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1764" s="10" t="s">
         <v>6376</v>
       </c>
-      <c r="E1764" s="4" t="s">
+      <c r="E1764" s="11" t="s">
         <v>6375</v>
       </c>
     </row>
@@ -53863,20 +53869,20 @@
         <v>6403</v>
       </c>
     </row>
-    <row r="1772" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1772" s="1" t="s">
+    <row r="1772" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1772" s="9" t="s">
         <v>6405</v>
       </c>
-      <c r="B1772" s="1" t="s">
+      <c r="B1772" s="9" t="s">
         <v>6406</v>
       </c>
-      <c r="C1772" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1772" s="2" t="s">
+      <c r="C1772" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1772" s="10" t="s">
         <v>6408</v>
       </c>
-      <c r="E1772" s="4" t="s">
+      <c r="E1772" s="11" t="s">
         <v>6407</v>
       </c>
     </row>
@@ -53931,20 +53937,20 @@
         <v>6419</v>
       </c>
     </row>
-    <row r="1776" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1776" s="1" t="s">
+    <row r="1776" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1776" s="9" t="s">
         <v>6421</v>
       </c>
-      <c r="B1776" s="1" t="s">
+      <c r="B1776" s="9" t="s">
         <v>6422</v>
       </c>
-      <c r="C1776" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1776" s="2" t="s">
+      <c r="C1776" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1776" s="10" t="s">
         <v>6424</v>
       </c>
-      <c r="E1776" s="4" t="s">
+      <c r="E1776" s="11" t="s">
         <v>6423</v>
       </c>
     </row>
@@ -53965,88 +53971,88 @@
         <v>6427</v>
       </c>
     </row>
-    <row r="1778" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1778" s="1" t="s">
+    <row r="1778" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1778" s="9" t="s">
         <v>6429</v>
       </c>
-      <c r="B1778" s="1" t="s">
+      <c r="B1778" s="9" t="s">
         <v>6430</v>
       </c>
-      <c r="C1778" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1778" s="2" t="s">
+      <c r="C1778" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1778" s="10" t="s">
         <v>6432</v>
       </c>
-      <c r="E1778" s="4" t="s">
+      <c r="E1778" s="11" t="s">
         <v>6431</v>
       </c>
     </row>
-    <row r="1779" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1779" s="1" t="s">
+    <row r="1779" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1779" s="9" t="s">
         <v>6433</v>
       </c>
-      <c r="B1779" s="1" t="s">
+      <c r="B1779" s="9" t="s">
         <v>6434</v>
       </c>
-      <c r="C1779" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1779" s="2" t="s">
+      <c r="C1779" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1779" s="10" t="s">
         <v>6436</v>
       </c>
-      <c r="E1779" s="4" t="s">
+      <c r="E1779" s="11" t="s">
         <v>6435</v>
       </c>
     </row>
-    <row r="1780" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1780" s="1" t="s">
+    <row r="1780" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1780" s="9" t="s">
         <v>6437</v>
       </c>
-      <c r="B1780" s="1" t="s">
+      <c r="B1780" s="9" t="s">
         <v>6438</v>
       </c>
-      <c r="C1780" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1780" s="2" t="s">
+      <c r="C1780" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1780" s="10" t="s">
         <v>6440</v>
       </c>
-      <c r="E1780" s="4" t="s">
+      <c r="E1780" s="11" t="s">
         <v>6439</v>
       </c>
     </row>
-    <row r="1781" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1781" s="1" t="s">
+    <row r="1781" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1781" s="9" t="s">
         <v>6441</v>
       </c>
-      <c r="B1781" s="1" t="s">
+      <c r="B1781" s="9" t="s">
         <v>6442</v>
       </c>
-      <c r="C1781" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1781" s="2" t="s">
+      <c r="C1781" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1781" s="10" t="s">
         <v>6444</v>
       </c>
-      <c r="E1781" s="4" t="s">
+      <c r="E1781" s="11" t="s">
         <v>6443</v>
       </c>
     </row>
-    <row r="1782" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1782" s="1" t="s">
+    <row r="1782" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1782" s="9" t="s">
         <v>6445</v>
       </c>
-      <c r="B1782" s="1" t="s">
+      <c r="B1782" s="9" t="s">
         <v>6446</v>
       </c>
-      <c r="C1782" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1782" s="2" t="s">
+      <c r="C1782" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1782" s="10" t="s">
         <v>6448</v>
       </c>
-      <c r="E1782" s="4" t="s">
+      <c r="E1782" s="11" t="s">
         <v>6447</v>
       </c>
     </row>
@@ -54115,207 +54121,207 @@
         <v>6461</v>
       </c>
     </row>
-    <row r="1787" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1787" s="1" t="s">
+    <row r="1787" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1787" s="9" t="s">
         <v>6463</v>
       </c>
-      <c r="B1787" s="1" t="s">
+      <c r="B1787" s="9" t="s">
         <v>6464</v>
       </c>
-      <c r="C1787" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1787" s="2">
+      <c r="C1787" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1787" s="10">
         <v>0</v>
       </c>
-      <c r="E1787" s="4" t="s">
+      <c r="E1787" s="11" t="s">
         <v>6465</v>
       </c>
     </row>
-    <row r="1788" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1788" s="1" t="s">
+    <row r="1788" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1788" s="9" t="s">
         <v>6466</v>
       </c>
-      <c r="B1788" s="1" t="s">
+      <c r="B1788" s="9" t="s">
         <v>6467</v>
       </c>
-      <c r="C1788" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1788" s="2">
+      <c r="C1788" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1788" s="10">
         <v>0</v>
       </c>
-      <c r="E1788" s="4" t="s">
+      <c r="E1788" s="11" t="s">
         <v>6468</v>
       </c>
     </row>
-    <row r="1789" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1789" s="1" t="s">
+    <row r="1789" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1789" s="9" t="s">
         <v>6469</v>
       </c>
-      <c r="B1789" s="1" t="s">
+      <c r="B1789" s="9" t="s">
         <v>6470</v>
       </c>
-      <c r="C1789" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1789" s="2" t="s">
+      <c r="C1789" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1789" s="10" t="s">
         <v>6472</v>
       </c>
-      <c r="E1789" s="4" t="s">
+      <c r="E1789" s="11" t="s">
         <v>6471</v>
       </c>
     </row>
-    <row r="1790" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1790" s="1" t="s">
+    <row r="1790" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1790" s="9" t="s">
         <v>6473</v>
       </c>
-      <c r="B1790" s="1" t="s">
+      <c r="B1790" s="9" t="s">
         <v>6251</v>
       </c>
-      <c r="C1790" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1790" s="2" t="s">
+      <c r="C1790" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1790" s="10" t="s">
         <v>6475</v>
       </c>
-      <c r="E1790" s="4" t="s">
+      <c r="E1790" s="11" t="s">
         <v>6474</v>
       </c>
     </row>
-    <row r="1791" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1791" s="1" t="s">
+    <row r="1791" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1791" s="9" t="s">
         <v>6476</v>
       </c>
-      <c r="B1791" s="1" t="s">
+      <c r="B1791" s="9" t="s">
         <v>6477</v>
       </c>
-      <c r="C1791" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1791" s="2" t="s">
+      <c r="C1791" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1791" s="10" t="s">
         <v>6479</v>
       </c>
-      <c r="E1791" s="4" t="s">
+      <c r="E1791" s="11" t="s">
         <v>6478</v>
       </c>
     </row>
-    <row r="1792" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1792" s="1" t="s">
+    <row r="1792" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1792" s="9" t="s">
         <v>6480</v>
       </c>
-      <c r="B1792" s="1" t="s">
+      <c r="B1792" s="9" t="s">
         <v>6481</v>
       </c>
-      <c r="C1792" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1792" s="2" t="s">
+      <c r="C1792" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1792" s="10" t="s">
         <v>6483</v>
       </c>
-      <c r="E1792" s="4" t="s">
+      <c r="E1792" s="11" t="s">
         <v>6482</v>
       </c>
     </row>
-    <row r="1793" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1793" s="1" t="s">
+    <row r="1793" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1793" s="9" t="s">
         <v>6484</v>
       </c>
-      <c r="B1793" s="1" t="s">
+      <c r="B1793" s="9" t="s">
         <v>6485</v>
       </c>
-      <c r="C1793" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1793" s="2" t="s">
+      <c r="C1793" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1793" s="10" t="s">
         <v>6487</v>
       </c>
-      <c r="E1793" s="4" t="s">
+      <c r="E1793" s="11" t="s">
         <v>6486</v>
       </c>
     </row>
-    <row r="1794" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1794" s="1" t="s">
+    <row r="1794" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1794" s="9" t="s">
         <v>6488</v>
       </c>
-      <c r="B1794" s="1" t="s">
+      <c r="B1794" s="9" t="s">
         <v>6489</v>
       </c>
-      <c r="C1794" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1794" s="2" t="s">
+      <c r="C1794" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1794" s="10" t="s">
         <v>6491</v>
       </c>
-      <c r="E1794" s="4" t="s">
+      <c r="E1794" s="11" t="s">
         <v>6490</v>
       </c>
     </row>
-    <row r="1795" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1795" s="1" t="s">
+    <row r="1795" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1795" s="9" t="s">
         <v>6492</v>
       </c>
-      <c r="B1795" s="1" t="s">
+      <c r="B1795" s="9" t="s">
         <v>6493</v>
       </c>
-      <c r="C1795" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1795" s="2" t="s">
+      <c r="C1795" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1795" s="10" t="s">
         <v>6495</v>
       </c>
-      <c r="E1795" s="4" t="s">
+      <c r="E1795" s="11" t="s">
         <v>6494</v>
       </c>
     </row>
-    <row r="1796" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1796" s="1" t="s">
+    <row r="1796" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1796" s="9" t="s">
         <v>6496</v>
       </c>
-      <c r="B1796" s="1" t="s">
+      <c r="B1796" s="9" t="s">
         <v>6497</v>
       </c>
-      <c r="C1796" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1796" s="2" t="s">
+      <c r="C1796" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1796" s="10" t="s">
         <v>6499</v>
       </c>
-      <c r="E1796" s="4" t="s">
+      <c r="E1796" s="11" t="s">
         <v>6498</v>
       </c>
     </row>
-    <row r="1797" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1797" s="1" t="s">
+    <row r="1797" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1797" s="9" t="s">
         <v>6500</v>
       </c>
-      <c r="B1797" s="1" t="s">
+      <c r="B1797" s="9" t="s">
         <v>6501</v>
       </c>
-      <c r="C1797" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1797" s="2">
+      <c r="C1797" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1797" s="10">
         <v>0</v>
       </c>
-      <c r="E1797" s="4" t="s">
+      <c r="E1797" s="11" t="s">
         <v>6502</v>
       </c>
     </row>
-    <row r="1798" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1798" s="1" t="s">
+    <row r="1798" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1798" s="9" t="s">
         <v>6503</v>
       </c>
-      <c r="B1798" s="1" t="s">
+      <c r="B1798" s="9" t="s">
         <v>6504</v>
       </c>
-      <c r="C1798" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1798" s="2">
+      <c r="C1798" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1798" s="10">
         <v>0</v>
       </c>
-      <c r="E1798" s="4" t="s">
+      <c r="E1798" s="11" t="s">
         <v>6505</v>
       </c>
     </row>
@@ -54336,156 +54342,156 @@
         <v>6508</v>
       </c>
     </row>
-    <row r="1800" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1800" s="1" t="s">
+    <row r="1800" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1800" s="9" t="s">
         <v>6509</v>
       </c>
-      <c r="B1800" s="1" t="s">
+      <c r="B1800" s="9" t="s">
         <v>6510</v>
       </c>
-      <c r="C1800" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1800" s="2">
+      <c r="C1800" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1800" s="10">
         <v>0</v>
       </c>
-      <c r="E1800" s="4" t="s">
+      <c r="E1800" s="11" t="s">
         <v>6511</v>
       </c>
     </row>
-    <row r="1801" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1801" s="1" t="s">
+    <row r="1801" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1801" s="9" t="s">
         <v>6512</v>
       </c>
-      <c r="B1801" s="1" t="s">
+      <c r="B1801" s="9" t="s">
         <v>6513</v>
       </c>
-      <c r="C1801" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1801" s="2" t="s">
+      <c r="C1801" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1801" s="10" t="s">
         <v>6515</v>
       </c>
-      <c r="E1801" s="4" t="s">
+      <c r="E1801" s="11" t="s">
         <v>6514</v>
       </c>
     </row>
-    <row r="1802" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1802" s="1" t="s">
+    <row r="1802" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1802" s="9" t="s">
         <v>6516</v>
       </c>
-      <c r="B1802" s="1" t="s">
+      <c r="B1802" s="9" t="s">
         <v>6517</v>
       </c>
-      <c r="C1802" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1802" s="2" t="s">
+      <c r="C1802" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1802" s="10" t="s">
         <v>6519</v>
       </c>
-      <c r="E1802" s="4" t="s">
+      <c r="E1802" s="11" t="s">
         <v>6518</v>
       </c>
     </row>
-    <row r="1803" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1803" s="1" t="s">
+    <row r="1803" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1803" s="9" t="s">
         <v>6520</v>
       </c>
-      <c r="B1803" s="1" t="s">
+      <c r="B1803" s="9" t="s">
         <v>6521</v>
       </c>
-      <c r="C1803" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1803" s="2">
+      <c r="C1803" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1803" s="10">
         <v>0</v>
       </c>
-      <c r="E1803" s="4" t="s">
+      <c r="E1803" s="11" t="s">
         <v>6522</v>
       </c>
     </row>
-    <row r="1804" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1804" s="1" t="s">
+    <row r="1804" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1804" s="9" t="s">
         <v>6523</v>
       </c>
-      <c r="B1804" s="1" t="s">
+      <c r="B1804" s="9" t="s">
         <v>6524</v>
       </c>
-      <c r="C1804" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1804" s="2">
+      <c r="C1804" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1804" s="10">
         <v>0</v>
       </c>
-      <c r="E1804" s="4" t="s">
+      <c r="E1804" s="11" t="s">
         <v>6525</v>
       </c>
     </row>
-    <row r="1805" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1805" s="1" t="s">
+    <row r="1805" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1805" s="9" t="s">
         <v>6526</v>
       </c>
-      <c r="B1805" s="1" t="s">
+      <c r="B1805" s="9" t="s">
         <v>6527</v>
       </c>
-      <c r="C1805" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1805" s="2">
+      <c r="C1805" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1805" s="10">
         <v>0</v>
       </c>
-      <c r="E1805" s="4" t="s">
+      <c r="E1805" s="11" t="s">
         <v>6528</v>
       </c>
     </row>
-    <row r="1806" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1806" s="1" t="s">
+    <row r="1806" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1806" s="9" t="s">
         <v>6529</v>
       </c>
-      <c r="B1806" s="1" t="s">
+      <c r="B1806" s="9" t="s">
         <v>6530</v>
       </c>
-      <c r="C1806" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1806" s="2" t="s">
+      <c r="C1806" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1806" s="10" t="s">
         <v>6532</v>
       </c>
-      <c r="E1806" s="4" t="s">
+      <c r="E1806" s="11" t="s">
         <v>6531</v>
       </c>
     </row>
-    <row r="1807" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1807" s="1" t="s">
+    <row r="1807" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1807" s="9" t="s">
         <v>6533</v>
       </c>
-      <c r="B1807" s="1" t="s">
+      <c r="B1807" s="9" t="s">
         <v>6534</v>
       </c>
-      <c r="C1807" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1807" s="2">
+      <c r="C1807" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1807" s="10">
         <v>0</v>
       </c>
-      <c r="E1807" s="4" t="s">
+      <c r="E1807" s="11" t="s">
         <v>6535</v>
       </c>
     </row>
-    <row r="1808" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1808" s="1" t="s">
+    <row r="1808" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1808" s="9" t="s">
         <v>6536</v>
       </c>
-      <c r="B1808" s="1" t="s">
+      <c r="B1808" s="9" t="s">
         <v>6537</v>
       </c>
-      <c r="C1808" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1808" s="2">
+      <c r="C1808" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1808" s="10">
         <v>0</v>
       </c>
-      <c r="E1808" s="4" t="s">
+      <c r="E1808" s="11" t="s">
         <v>6538</v>
       </c>
     </row>
@@ -54608,20 +54614,20 @@
         <v>6563</v>
       </c>
     </row>
-    <row r="1816" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1816" s="1" t="s">
+    <row r="1816" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1816" s="9" t="s">
         <v>6565</v>
       </c>
-      <c r="B1816" s="1" t="s">
+      <c r="B1816" s="9" t="s">
         <v>6566</v>
       </c>
-      <c r="C1816" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1816" s="2" t="s">
+      <c r="C1816" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1816" s="10" t="s">
         <v>6568</v>
       </c>
-      <c r="E1816" s="4" t="s">
+      <c r="E1816" s="11" t="s">
         <v>6567</v>
       </c>
     </row>
@@ -54931,20 +54937,20 @@
         <v>6639</v>
       </c>
     </row>
-    <row r="1835" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1835" s="1" t="s">
+    <row r="1835" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1835" s="9" t="s">
         <v>6641</v>
       </c>
-      <c r="B1835" s="1" t="s">
+      <c r="B1835" s="9" t="s">
         <v>6642</v>
       </c>
-      <c r="C1835" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1835" s="2">
+      <c r="C1835" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1835" s="10">
         <v>0</v>
       </c>
-      <c r="E1835" s="4" t="s">
+      <c r="E1835" s="11" t="s">
         <v>6643</v>
       </c>
     </row>
@@ -54965,37 +54971,37 @@
         <v>6646</v>
       </c>
     </row>
-    <row r="1837" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1837" s="1" t="s">
+    <row r="1837" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1837" s="9" t="s">
         <v>6648</v>
       </c>
-      <c r="B1837" s="1" t="s">
+      <c r="B1837" s="9" t="s">
         <v>6649</v>
       </c>
-      <c r="C1837" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1837" s="2" t="s">
+      <c r="C1837" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1837" s="10" t="s">
         <v>6651</v>
       </c>
-      <c r="E1837" s="4" t="s">
+      <c r="E1837" s="11" t="s">
         <v>6650</v>
       </c>
     </row>
-    <row r="1838" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1838" s="1" t="s">
+    <row r="1838" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1838" s="9" t="s">
         <v>6652</v>
       </c>
-      <c r="B1838" s="1" t="s">
+      <c r="B1838" s="9" t="s">
         <v>6653</v>
       </c>
-      <c r="C1838" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1838" s="2" t="s">
+      <c r="C1838" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1838" s="10" t="s">
         <v>6655</v>
       </c>
-      <c r="E1838" s="4" t="s">
+      <c r="E1838" s="11" t="s">
         <v>6654</v>
       </c>
     </row>
@@ -55084,20 +55090,20 @@
         <v>6673</v>
       </c>
     </row>
-    <row r="1844" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1844" s="1" t="s">
+    <row r="1844" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1844" s="9" t="s">
         <v>6675</v>
       </c>
-      <c r="B1844" s="1" t="s">
+      <c r="B1844" s="9" t="s">
         <v>6676</v>
       </c>
-      <c r="C1844" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1844" s="2" t="s">
+      <c r="C1844" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1844" s="10" t="s">
         <v>6678</v>
       </c>
-      <c r="E1844" s="4" t="s">
+      <c r="E1844" s="11" t="s">
         <v>6677</v>
       </c>
     </row>
@@ -55135,88 +55141,88 @@
         <v>6685</v>
       </c>
     </row>
-    <row r="1847" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1847" s="1" t="s">
+    <row r="1847" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1847" s="9" t="s">
         <v>6687</v>
       </c>
-      <c r="B1847" s="1" t="s">
+      <c r="B1847" s="9" t="s">
         <v>6688</v>
       </c>
-      <c r="C1847" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1847" s="2" t="s">
+      <c r="C1847" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1847" s="10" t="s">
         <v>6690</v>
       </c>
-      <c r="E1847" s="4" t="s">
+      <c r="E1847" s="11" t="s">
         <v>6689</v>
       </c>
     </row>
-    <row r="1848" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1848" s="1" t="s">
+    <row r="1848" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1848" s="9" t="s">
         <v>6691</v>
       </c>
-      <c r="B1848" s="1" t="s">
+      <c r="B1848" s="9" t="s">
         <v>6692</v>
       </c>
-      <c r="C1848" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1848" s="2" t="s">
+      <c r="C1848" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1848" s="10" t="s">
         <v>6694</v>
       </c>
-      <c r="E1848" s="4" t="s">
+      <c r="E1848" s="11" t="s">
         <v>6693</v>
       </c>
     </row>
-    <row r="1849" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1849" s="1" t="s">
+    <row r="1849" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1849" s="9" t="s">
         <v>6695</v>
       </c>
-      <c r="B1849" s="1" t="s">
+      <c r="B1849" s="9" t="s">
         <v>6696</v>
       </c>
-      <c r="C1849" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1849" s="2" t="s">
+      <c r="C1849" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1849" s="10" t="s">
         <v>6697</v>
       </c>
-      <c r="E1849" s="4" t="s">
+      <c r="E1849" s="11" t="s">
         <v>6693</v>
       </c>
     </row>
-    <row r="1850" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1850" s="1" t="s">
+    <row r="1850" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1850" s="9" t="s">
         <v>6698</v>
       </c>
-      <c r="B1850" s="1" t="s">
+      <c r="B1850" s="9" t="s">
         <v>6699</v>
       </c>
-      <c r="C1850" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1850" s="2" t="s">
+      <c r="C1850" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1850" s="10" t="s">
         <v>6701</v>
       </c>
-      <c r="E1850" s="4" t="s">
+      <c r="E1850" s="11" t="s">
         <v>6700</v>
       </c>
     </row>
-    <row r="1851" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1851" s="1" t="s">
+    <row r="1851" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1851" s="9" t="s">
         <v>6702</v>
       </c>
-      <c r="B1851" s="1" t="s">
+      <c r="B1851" s="9" t="s">
         <v>6703</v>
       </c>
-      <c r="C1851" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1851" s="2" t="s">
+      <c r="C1851" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1851" s="10" t="s">
         <v>6705</v>
       </c>
-      <c r="E1851" s="4" t="s">
+      <c r="E1851" s="11" t="s">
         <v>6704</v>
       </c>
     </row>
@@ -55254,258 +55260,258 @@
         <v>6712</v>
       </c>
     </row>
-    <row r="1854" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1854" s="1" t="s">
+    <row r="1854" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1854" s="9" t="s">
         <v>6714</v>
       </c>
-      <c r="B1854" s="1" t="s">
+      <c r="B1854" s="9" t="s">
         <v>6715</v>
       </c>
-      <c r="C1854" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1854" s="2" t="s">
+      <c r="C1854" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1854" s="10" t="s">
         <v>6717</v>
       </c>
-      <c r="E1854" s="4" t="s">
+      <c r="E1854" s="11" t="s">
         <v>6716</v>
       </c>
     </row>
-    <row r="1855" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1855" s="1" t="s">
+    <row r="1855" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1855" s="9" t="s">
         <v>6718</v>
       </c>
-      <c r="B1855" s="1" t="s">
+      <c r="B1855" s="9" t="s">
         <v>6719</v>
       </c>
-      <c r="C1855" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1855" s="2" t="s">
+      <c r="C1855" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1855" s="10" t="s">
         <v>6721</v>
       </c>
-      <c r="E1855" s="4" t="s">
+      <c r="E1855" s="11" t="s">
         <v>6720</v>
       </c>
     </row>
-    <row r="1856" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1856" s="1" t="s">
+    <row r="1856" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1856" s="9" t="s">
         <v>6722</v>
       </c>
-      <c r="B1856" s="1" t="s">
+      <c r="B1856" s="9" t="s">
         <v>6723</v>
       </c>
-      <c r="C1856" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1856" s="2" t="s">
+      <c r="C1856" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1856" s="10" t="s">
         <v>6725</v>
       </c>
-      <c r="E1856" s="4" t="s">
+      <c r="E1856" s="11" t="s">
         <v>6724</v>
       </c>
     </row>
-    <row r="1857" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1857" s="1" t="s">
+    <row r="1857" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1857" s="9" t="s">
         <v>6726</v>
       </c>
-      <c r="B1857" s="1" t="s">
+      <c r="B1857" s="9" t="s">
         <v>6727</v>
       </c>
-      <c r="C1857" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1857" s="2" t="s">
+      <c r="C1857" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1857" s="10" t="s">
         <v>6729</v>
       </c>
-      <c r="E1857" s="4" t="s">
+      <c r="E1857" s="11" t="s">
         <v>6728</v>
       </c>
     </row>
-    <row r="1858" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1858" s="1" t="s">
+    <row r="1858" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1858" s="9" t="s">
         <v>6730</v>
       </c>
-      <c r="B1858" s="1" t="s">
+      <c r="B1858" s="9" t="s">
         <v>6731</v>
       </c>
-      <c r="C1858" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1858" s="2">
+      <c r="C1858" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1858" s="10">
         <v>0</v>
       </c>
-      <c r="E1858" s="4" t="s">
+      <c r="E1858" s="11" t="s">
         <v>6732</v>
       </c>
     </row>
-    <row r="1859" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1859" s="1" t="s">
+    <row r="1859" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1859" s="9" t="s">
         <v>6733</v>
       </c>
-      <c r="B1859" s="1" t="s">
+      <c r="B1859" s="9" t="s">
         <v>6734</v>
       </c>
-      <c r="C1859" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1859" s="2">
+      <c r="C1859" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1859" s="10">
         <v>0</v>
       </c>
-      <c r="E1859" s="4" t="s">
+      <c r="E1859" s="11" t="s">
         <v>6735</v>
       </c>
     </row>
-    <row r="1860" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1860" s="1" t="s">
+    <row r="1860" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1860" s="9" t="s">
         <v>6736</v>
       </c>
-      <c r="B1860" s="1" t="s">
+      <c r="B1860" s="9" t="s">
         <v>6737</v>
       </c>
-      <c r="C1860" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1860" s="2" t="s">
+      <c r="C1860" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1860" s="10" t="s">
         <v>6739</v>
       </c>
-      <c r="E1860" s="4" t="s">
+      <c r="E1860" s="11" t="s">
         <v>6738</v>
       </c>
     </row>
-    <row r="1861" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1861" s="1" t="s">
+    <row r="1861" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1861" s="9" t="s">
         <v>6740</v>
       </c>
-      <c r="B1861" s="1" t="s">
+      <c r="B1861" s="9" t="s">
         <v>6741</v>
       </c>
-      <c r="C1861" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1861" s="2" t="s">
+      <c r="C1861" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1861" s="10" t="s">
         <v>6743</v>
       </c>
-      <c r="E1861" s="4" t="s">
+      <c r="E1861" s="11" t="s">
         <v>6742</v>
       </c>
     </row>
-    <row r="1862" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1862" s="1" t="s">
+    <row r="1862" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1862" s="9" t="s">
         <v>6744</v>
       </c>
-      <c r="B1862" s="1" t="s">
+      <c r="B1862" s="9" t="s">
         <v>6745</v>
       </c>
-      <c r="C1862" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1862" s="2">
+      <c r="C1862" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1862" s="10">
         <v>0</v>
       </c>
-      <c r="E1862" s="4" t="s">
+      <c r="E1862" s="11" t="s">
         <v>6746</v>
       </c>
     </row>
-    <row r="1863" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1863" s="1" t="s">
+    <row r="1863" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1863" s="9" t="s">
         <v>6747</v>
       </c>
-      <c r="B1863" s="1" t="s">
+      <c r="B1863" s="9" t="s">
         <v>6748</v>
       </c>
-      <c r="C1863" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1863" s="2" t="s">
+      <c r="C1863" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1863" s="10" t="s">
         <v>6750</v>
       </c>
-      <c r="E1863" s="4" t="s">
+      <c r="E1863" s="11" t="s">
         <v>6749</v>
       </c>
     </row>
-    <row r="1864" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1864" s="1" t="s">
+    <row r="1864" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1864" s="9" t="s">
         <v>6751</v>
       </c>
-      <c r="B1864" s="1" t="s">
+      <c r="B1864" s="9" t="s">
         <v>6752</v>
       </c>
-      <c r="C1864" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1864" s="2" t="s">
+      <c r="C1864" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1864" s="10" t="s">
         <v>6754</v>
       </c>
-      <c r="E1864" s="4" t="s">
+      <c r="E1864" s="11" t="s">
         <v>6753</v>
       </c>
     </row>
-    <row r="1865" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1865" s="1" t="s">
+    <row r="1865" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1865" s="9" t="s">
         <v>6755</v>
       </c>
-      <c r="B1865" s="1" t="s">
+      <c r="B1865" s="9" t="s">
         <v>6756</v>
       </c>
-      <c r="C1865" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1865" s="2" t="s">
+      <c r="C1865" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1865" s="10" t="s">
         <v>6758</v>
       </c>
-      <c r="E1865" s="4" t="s">
+      <c r="E1865" s="11" t="s">
         <v>6757</v>
       </c>
     </row>
-    <row r="1866" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1866" s="1" t="s">
+    <row r="1866" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1866" s="9" t="s">
         <v>6759</v>
       </c>
-      <c r="B1866" s="1" t="s">
+      <c r="B1866" s="9" t="s">
         <v>6760</v>
       </c>
-      <c r="C1866" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1866" s="2" t="s">
+      <c r="C1866" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1866" s="10" t="s">
         <v>6762</v>
       </c>
-      <c r="E1866" s="4" t="s">
+      <c r="E1866" s="11" t="s">
         <v>6761</v>
       </c>
     </row>
-    <row r="1867" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1867" s="1" t="s">
+    <row r="1867" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1867" s="9" t="s">
         <v>6763</v>
       </c>
-      <c r="B1867" s="1" t="s">
+      <c r="B1867" s="9" t="s">
         <v>6764</v>
       </c>
-      <c r="C1867" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1867" s="2" t="s">
+      <c r="C1867" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1867" s="10" t="s">
         <v>6766</v>
       </c>
-      <c r="E1867" s="4" t="s">
+      <c r="E1867" s="11" t="s">
         <v>6765</v>
       </c>
     </row>
-    <row r="1868" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1868" s="1" t="s">
+    <row r="1868" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1868" s="9" t="s">
         <v>6767</v>
       </c>
-      <c r="B1868" s="1" t="s">
+      <c r="B1868" s="9" t="s">
         <v>6768</v>
       </c>
-      <c r="C1868" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1868" s="2">
+      <c r="C1868" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1868" s="10">
         <v>0</v>
       </c>
-      <c r="E1868" s="4" t="s">
+      <c r="E1868" s="11" t="s">
         <v>6765</v>
       </c>
     </row>
@@ -55526,20 +55532,20 @@
         <v>6771</v>
       </c>
     </row>
-    <row r="1870" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1870" s="1" t="s">
+    <row r="1870" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1870" s="9" t="s">
         <v>6773</v>
       </c>
-      <c r="B1870" s="1" t="s">
+      <c r="B1870" s="9" t="s">
         <v>6774</v>
       </c>
-      <c r="C1870" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1870" s="2" t="s">
+      <c r="C1870" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1870" s="10" t="s">
         <v>6776</v>
       </c>
-      <c r="E1870" s="4" t="s">
+      <c r="E1870" s="11" t="s">
         <v>6775</v>
       </c>
     </row>
@@ -55679,20 +55685,20 @@
         <v>6807</v>
       </c>
     </row>
-    <row r="1879" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1879" s="1" t="s">
+    <row r="1879" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1879" s="9" t="s">
         <v>6809</v>
       </c>
-      <c r="B1879" s="1" t="s">
+      <c r="B1879" s="9" t="s">
         <v>6810</v>
       </c>
-      <c r="C1879" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1879" s="2" t="s">
+      <c r="C1879" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1879" s="10" t="s">
         <v>6812</v>
       </c>
-      <c r="E1879" s="4" t="s">
+      <c r="E1879" s="11" t="s">
         <v>6811</v>
       </c>
     </row>
@@ -55713,20 +55719,20 @@
         <v>6815</v>
       </c>
     </row>
-    <row r="1881" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1881" s="1" t="s">
+    <row r="1881" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1881" s="9" t="s">
         <v>6817</v>
       </c>
-      <c r="B1881" s="1" t="s">
+      <c r="B1881" s="9" t="s">
         <v>6818</v>
       </c>
-      <c r="C1881" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1881" s="2" t="s">
+      <c r="C1881" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1881" s="10" t="s">
         <v>6820</v>
       </c>
-      <c r="E1881" s="4" t="s">
+      <c r="E1881" s="11" t="s">
         <v>6819</v>
       </c>
     </row>
@@ -55781,20 +55787,20 @@
         <v>6831</v>
       </c>
     </row>
-    <row r="1885" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1885" s="1" t="s">
+    <row r="1885" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1885" s="9" t="s">
         <v>6833</v>
       </c>
-      <c r="B1885" s="1" t="s">
+      <c r="B1885" s="9" t="s">
         <v>6834</v>
       </c>
-      <c r="C1885" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1885" s="2" t="s">
+      <c r="C1885" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1885" s="10" t="s">
         <v>6836</v>
       </c>
-      <c r="E1885" s="4" t="s">
+      <c r="E1885" s="11" t="s">
         <v>6835</v>
       </c>
     </row>
@@ -55883,20 +55889,20 @@
         <v>6855</v>
       </c>
     </row>
-    <row r="1891" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1891" s="1" t="s">
+    <row r="1891" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1891" s="9" t="s">
         <v>6857</v>
       </c>
-      <c r="B1891" s="1" t="s">
+      <c r="B1891" s="9" t="s">
         <v>6858</v>
       </c>
-      <c r="C1891" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1891" s="2" t="s">
+      <c r="C1891" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1891" s="10" t="s">
         <v>6860</v>
       </c>
-      <c r="E1891" s="4" t="s">
+      <c r="E1891" s="11" t="s">
         <v>6859</v>
       </c>
     </row>
@@ -55934,20 +55940,20 @@
         <v>6867</v>
       </c>
     </row>
-    <row r="1894" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1894" s="1" t="s">
+    <row r="1894" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1894" s="9" t="s">
         <v>6869</v>
       </c>
-      <c r="B1894" s="1" t="s">
+      <c r="B1894" s="9" t="s">
         <v>6870</v>
       </c>
-      <c r="C1894" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1894" s="2" t="s">
+      <c r="C1894" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1894" s="10" t="s">
         <v>6872</v>
       </c>
-      <c r="E1894" s="4" t="s">
+      <c r="E1894" s="11" t="s">
         <v>6871</v>
       </c>
     </row>
@@ -56172,20 +56178,20 @@
         <v>6923</v>
       </c>
     </row>
-    <row r="1908" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1908" s="1" t="s">
+    <row r="1908" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1908" s="9" t="s">
         <v>6925</v>
       </c>
-      <c r="B1908" s="1" t="s">
+      <c r="B1908" s="9" t="s">
         <v>6926</v>
       </c>
-      <c r="C1908" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1908" s="2" t="s">
+      <c r="C1908" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1908" s="10" t="s">
         <v>6928</v>
       </c>
-      <c r="E1908" s="4" t="s">
+      <c r="E1908" s="11" t="s">
         <v>6927</v>
       </c>
     </row>
@@ -57036,20 +57042,20 @@
         <v>7123</v>
       </c>
     </row>
-    <row r="1959" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1959" s="1" t="s">
+    <row r="1959" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1959" s="9" t="s">
         <v>7125</v>
       </c>
-      <c r="B1959" s="1" t="s">
+      <c r="B1959" s="9" t="s">
         <v>7126</v>
       </c>
-      <c r="C1959" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1959" s="2" t="s">
+      <c r="C1959" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1959" s="10" t="s">
         <v>7128</v>
       </c>
-      <c r="E1959" s="4" t="s">
+      <c r="E1959" s="11" t="s">
         <v>7127</v>
       </c>
     </row>
@@ -57070,37 +57076,37 @@
         <v>7131</v>
       </c>
     </row>
-    <row r="1961" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1961" s="1" t="s">
+    <row r="1961" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1961" s="9" t="s">
         <v>7133</v>
       </c>
-      <c r="B1961" s="1" t="s">
+      <c r="B1961" s="9" t="s">
         <v>7134</v>
       </c>
-      <c r="C1961" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1961" s="2" t="s">
+      <c r="C1961" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1961" s="10" t="s">
         <v>7136</v>
       </c>
-      <c r="E1961" s="4" t="s">
+      <c r="E1961" s="11" t="s">
         <v>7135</v>
       </c>
     </row>
-    <row r="1962" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1962" s="1" t="s">
+    <row r="1962" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1962" s="9" t="s">
         <v>7137</v>
       </c>
-      <c r="B1962" s="1" t="s">
+      <c r="B1962" s="9" t="s">
         <v>7138</v>
       </c>
-      <c r="C1962" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1962" s="2" t="s">
+      <c r="C1962" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1962" s="10" t="s">
         <v>7140</v>
       </c>
-      <c r="E1962" s="4" t="s">
+      <c r="E1962" s="11" t="s">
         <v>7139</v>
       </c>
     </row>
@@ -57121,20 +57127,20 @@
         <v>7143</v>
       </c>
     </row>
-    <row r="1964" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1964" s="1" t="s">
+    <row r="1964" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1964" s="9" t="s">
         <v>7145</v>
       </c>
-      <c r="B1964" s="1" t="s">
+      <c r="B1964" s="9" t="s">
         <v>7146</v>
       </c>
-      <c r="C1964" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1964" s="2" t="s">
+      <c r="C1964" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1964" s="10" t="s">
         <v>7148</v>
       </c>
-      <c r="E1964" s="4" t="s">
+      <c r="E1964" s="11" t="s">
         <v>7147</v>
       </c>
     </row>
@@ -57359,20 +57365,20 @@
         <v>7199</v>
       </c>
     </row>
-    <row r="1978" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1978" s="1" t="s">
+    <row r="1978" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1978" s="9" t="s">
         <v>7201</v>
       </c>
-      <c r="B1978" s="1" t="s">
+      <c r="B1978" s="9" t="s">
         <v>7202</v>
       </c>
-      <c r="C1978" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1978" s="2" t="s">
+      <c r="C1978" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1978" s="10" t="s">
         <v>7204</v>
       </c>
-      <c r="E1978" s="4" t="s">
+      <c r="E1978" s="11" t="s">
         <v>7203</v>
       </c>
     </row>
@@ -57410,88 +57416,88 @@
         <v>7211</v>
       </c>
     </row>
-    <row r="1981" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1981" s="1" t="s">
+    <row r="1981" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1981" s="9" t="s">
         <v>7213</v>
       </c>
-      <c r="B1981" s="1" t="s">
+      <c r="B1981" s="9" t="s">
         <v>7214</v>
       </c>
-      <c r="C1981" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1981" s="2" t="s">
+      <c r="C1981" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1981" s="10" t="s">
         <v>7216</v>
       </c>
-      <c r="E1981" s="4" t="s">
+      <c r="E1981" s="11" t="s">
         <v>7215</v>
       </c>
     </row>
-    <row r="1982" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1982" s="1" t="s">
+    <row r="1982" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1982" s="9" t="s">
         <v>7217</v>
       </c>
-      <c r="B1982" s="1" t="s">
+      <c r="B1982" s="9" t="s">
         <v>7218</v>
       </c>
-      <c r="C1982" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1982" s="2" t="s">
+      <c r="C1982" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1982" s="10" t="s">
         <v>7220</v>
       </c>
-      <c r="E1982" s="4" t="s">
+      <c r="E1982" s="11" t="s">
         <v>7219</v>
       </c>
     </row>
-    <row r="1983" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1983" s="1" t="s">
+    <row r="1983" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1983" s="9" t="s">
         <v>7221</v>
       </c>
-      <c r="B1983" s="1" t="s">
+      <c r="B1983" s="9" t="s">
         <v>7222</v>
       </c>
-      <c r="C1983" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1983" s="2" t="s">
+      <c r="C1983" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1983" s="10" t="s">
         <v>7224</v>
       </c>
-      <c r="E1983" s="4" t="s">
+      <c r="E1983" s="11" t="s">
         <v>7223</v>
       </c>
     </row>
-    <row r="1984" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1984" s="1" t="s">
+    <row r="1984" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1984" s="9" t="s">
         <v>7225</v>
       </c>
-      <c r="B1984" s="1" t="s">
+      <c r="B1984" s="9" t="s">
         <v>7226</v>
       </c>
-      <c r="C1984" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1984" s="2" t="s">
+      <c r="C1984" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1984" s="10" t="s">
         <v>7228</v>
       </c>
-      <c r="E1984" s="4" t="s">
+      <c r="E1984" s="11" t="s">
         <v>7227</v>
       </c>
     </row>
-    <row r="1985" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A1985" s="1" t="s">
+    <row r="1985" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A1985" s="9" t="s">
         <v>7229</v>
       </c>
-      <c r="B1985" s="1" t="s">
+      <c r="B1985" s="9" t="s">
         <v>7230</v>
       </c>
-      <c r="C1985" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1985" s="2" t="s">
+      <c r="C1985" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1985" s="10" t="s">
         <v>7232</v>
       </c>
-      <c r="E1985" s="4" t="s">
+      <c r="E1985" s="11" t="s">
         <v>7231</v>
       </c>
     </row>
@@ -58243,88 +58249,88 @@
         <v>7398</v>
       </c>
     </row>
-    <row r="2030" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A2030" s="1" t="s">
+    <row r="2030" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A2030" s="9" t="s">
         <v>7400</v>
       </c>
-      <c r="B2030" s="1" t="s">
+      <c r="B2030" s="9" t="s">
         <v>7401</v>
       </c>
-      <c r="C2030" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2030" s="2" t="s">
+      <c r="C2030" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2030" s="10" t="s">
         <v>7403</v>
       </c>
-      <c r="E2030" s="4" t="s">
+      <c r="E2030" s="11" t="s">
         <v>7402</v>
       </c>
     </row>
-    <row r="2031" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A2031" s="1" t="s">
+    <row r="2031" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A2031" s="9" t="s">
         <v>7404</v>
       </c>
-      <c r="B2031" s="1" t="s">
+      <c r="B2031" s="9" t="s">
         <v>7405</v>
       </c>
-      <c r="C2031" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2031" s="2" t="s">
+      <c r="C2031" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2031" s="10" t="s">
         <v>7407</v>
       </c>
-      <c r="E2031" s="4" t="s">
+      <c r="E2031" s="11" t="s">
         <v>7406</v>
       </c>
     </row>
-    <row r="2032" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A2032" s="1" t="s">
+    <row r="2032" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A2032" s="9" t="s">
         <v>7408</v>
       </c>
-      <c r="B2032" s="1" t="s">
+      <c r="B2032" s="9" t="s">
         <v>7409</v>
       </c>
-      <c r="C2032" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2032" s="2" t="s">
+      <c r="C2032" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2032" s="10" t="s">
         <v>7411</v>
       </c>
-      <c r="E2032" s="4" t="s">
+      <c r="E2032" s="11" t="s">
         <v>7410</v>
       </c>
     </row>
-    <row r="2033" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A2033" s="1" t="s">
+    <row r="2033" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A2033" s="9" t="s">
         <v>7412</v>
       </c>
-      <c r="B2033" s="1" t="s">
+      <c r="B2033" s="9" t="s">
         <v>7413</v>
       </c>
-      <c r="C2033" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2033" s="2" t="s">
+      <c r="C2033" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2033" s="10" t="s">
         <v>7415</v>
       </c>
-      <c r="E2033" s="4" t="s">
+      <c r="E2033" s="11" t="s">
         <v>7414</v>
       </c>
     </row>
-    <row r="2034" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A2034" s="1" t="s">
+    <row r="2034" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A2034" s="9" t="s">
         <v>7416</v>
       </c>
-      <c r="B2034" s="1" t="s">
+      <c r="B2034" s="9" t="s">
         <v>7417</v>
       </c>
-      <c r="C2034" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2034" s="2" t="s">
+      <c r="C2034" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2034" s="10" t="s">
         <v>7419</v>
       </c>
-      <c r="E2034" s="4" t="s">
+      <c r="E2034" s="11" t="s">
         <v>7418</v>
       </c>
     </row>
@@ -59144,20 +59150,20 @@
         <v>7479</v>
       </c>
     </row>
-    <row r="2083" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A2083" s="1" t="s">
+    <row r="2083" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A2083" s="9" t="s">
         <v>7599</v>
       </c>
-      <c r="B2083" s="1" t="s">
+      <c r="B2083" s="9" t="s">
         <v>7600</v>
       </c>
-      <c r="C2083" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2083" s="2" t="s">
+      <c r="C2083" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2083" s="10" t="s">
         <v>7602</v>
       </c>
-      <c r="E2083" s="4" t="s">
+      <c r="E2083" s="11" t="s">
         <v>7601</v>
       </c>
     </row>
@@ -59399,37 +59405,37 @@
         <v>7422</v>
       </c>
     </row>
-    <row r="2098" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A2098" s="1" t="s">
+    <row r="2098" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A2098" s="9" t="s">
         <v>7654</v>
       </c>
-      <c r="B2098" s="1" t="s">
+      <c r="B2098" s="9" t="s">
         <v>7655</v>
       </c>
-      <c r="C2098" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2098" s="2" t="s">
+      <c r="C2098" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2098" s="10" t="s">
         <v>7657</v>
       </c>
-      <c r="E2098" s="4" t="s">
+      <c r="E2098" s="11" t="s">
         <v>7656</v>
       </c>
     </row>
-    <row r="2099" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A2099" s="1" t="s">
+    <row r="2099" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A2099" s="9" t="s">
         <v>7658</v>
       </c>
-      <c r="B2099" s="1" t="s">
+      <c r="B2099" s="9" t="s">
         <v>7659</v>
       </c>
-      <c r="C2099" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2099" s="2" t="s">
+      <c r="C2099" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2099" s="10" t="s">
         <v>7661</v>
       </c>
-      <c r="E2099" s="4" t="s">
+      <c r="E2099" s="11" t="s">
         <v>7660</v>
       </c>
     </row>
@@ -59450,20 +59456,20 @@
         <v>7664</v>
       </c>
     </row>
-    <row r="2101" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A2101" s="1" t="s">
+    <row r="2101" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A2101" s="9" t="s">
         <v>7666</v>
       </c>
-      <c r="B2101" s="1" t="s">
+      <c r="B2101" s="9" t="s">
         <v>7667</v>
       </c>
-      <c r="C2101" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2101" s="2" t="s">
+      <c r="C2101" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2101" s="10" t="s">
         <v>7669</v>
       </c>
-      <c r="E2101" s="4" t="s">
+      <c r="E2101" s="11" t="s">
         <v>7668</v>
       </c>
     </row>
@@ -59484,20 +59490,20 @@
         <v>7672</v>
       </c>
     </row>
-    <row r="2103" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A2103" s="1" t="s">
+    <row r="2103" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A2103" s="9" t="s">
         <v>7674</v>
       </c>
-      <c r="B2103" s="1" t="s">
+      <c r="B2103" s="9" t="s">
         <v>7675</v>
       </c>
-      <c r="C2103" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2103" s="2" t="s">
+      <c r="C2103" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2103" s="10" t="s">
         <v>7677</v>
       </c>
-      <c r="E2103" s="4" t="s">
+      <c r="E2103" s="11" t="s">
         <v>7676</v>
       </c>
     </row>
@@ -59552,20 +59558,20 @@
         <v>7688</v>
       </c>
     </row>
-    <row r="2107" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A2107" s="1" t="s">
+    <row r="2107" spans="1:5" s="12" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A2107" s="9" t="s">
         <v>7690</v>
       </c>
-      <c r="B2107" s="1" t="s">
+      <c r="B2107" s="9" t="s">
         <v>7691</v>
       </c>
-      <c r="C2107" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2107" s="2" t="s">
+      <c r="C2107" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2107" s="10" t="s">
         <v>7693</v>
       </c>
-      <c r="E2107" s="4" t="s">
+      <c r="E2107" s="11" t="s">
         <v>7692</v>
       </c>
     </row>
